--- a/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
+++ b/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
@@ -2,57 +2,36 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -67,16 +46,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -159,44 +135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -223,15 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -258,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -270,142 +244,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -415,20 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B183"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
-  <cols>
-    <col width="36.9140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="27" bestFit="1" customWidth="1" min="2" max="2"/>
-  </cols>
+  <dimension ref="A1:B184"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
@@ -1469,1156 +1463,1168 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TXT_EFFECTS</t>
+          <t>TXT_CYLINDER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>特效</t>
+          <t>圆柱体</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TXT_LIGHT</t>
+          <t>TXT_EFFECTS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>光照</t>
+          <t>特效</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TXT_AUDIO</t>
+          <t>TXT_LIGHT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>声音</t>
+          <t>光照</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TXT_VIDEO</t>
+          <t>TXT_AUDIO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>视频</t>
+          <t>声音</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TXT_UI</t>
+          <t>TXT_VIDEO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>视频</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TXT_UI_TOOLKIT</t>
+          <t>TXT_UI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UI 工具</t>
+          <t>UI</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TXT_CAMERA</t>
+          <t>TXT_UI_TOOLKIT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>相机</t>
+          <t>UI 工具</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TXT_VISUAL_SCRIPTING_SCENE_VARAIBLES</t>
+          <t>TXT_CAMERA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Visual Scripting Scene Varaibles</t>
+          <t>相机</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TXT_CENTER_ON_CHILDREN</t>
+          <t>TXT_VISUAL_SCRIPTING_SCENE_VARAIBLES</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Center On Children</t>
+          <t>Visual Scripting Scene Varaibles</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TXT_MAKE_PARENT</t>
+          <t>TXT_CENTER_ON_CHILDREN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Make Parent</t>
+          <t>Center On Children</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TXT_CLEAR_PARENT</t>
+          <t>TXT_MAKE_PARENT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Clear Parent</t>
+          <t>Make Parent</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TXT_SET_AS_FIRST_SIBLING</t>
+          <t>TXT_CLEAR_PARENT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Set as first sibling</t>
+          <t>Clear Parent</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TXT_SET_AS_LAST_SIBLING</t>
+          <t>TXT_SET_AS_FIRST_SIBLING</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Set as last sibling</t>
+          <t>Set as first sibling</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TXT_MOVE_TO_VIEW</t>
+          <t>TXT_SET_AS_LAST_SIBLING</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Move To View</t>
+          <t>Set as last sibling</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TXT_ALIGN_WITH_VIEW</t>
+          <t>TXT_MOVE_TO_VIEW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Align With View</t>
+          <t>Move To View</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TXT_ALIGN_VIEW_TO_SELECTED</t>
+          <t>TXT_ALIGN_WITH_VIEW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Align View to Selected</t>
+          <t>Align With View</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TXT_TOGGLE_ACTIVE_STATE</t>
+          <t>TXT_ALIGN_VIEW_TO_SELECTED</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Toggle Active State</t>
+          <t>Align View to Selected</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TXT_COMPONENT</t>
+          <t>TXT_TOGGLE_ACTIVE_STATE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>组件</t>
+          <t>Toggle Active State</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TXT_ADD</t>
+          <t>TXT_COMPONENT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>添加…</t>
+          <t>组件</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TXT_MESH</t>
+          <t>TXT_ADD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>网格</t>
+          <t>添加…</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TXT_PHYSICS</t>
+          <t>TXT_MESH</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>网格</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TXT_PHYSICS_2D</t>
+          <t>TXT_PHYSICS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Physics 2D</t>
+          <t>Physics</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TXT_NAVIGATION</t>
+          <t>TXT_PHYSICS_2D</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Physics 2D</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TXT_RENDERING</t>
+          <t>TXT_NAVIGATION</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rendering</t>
+          <t>Navigation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TXT_TILEMAP</t>
+          <t>TXT_RENDERING</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tilemap</t>
+          <t>Rendering</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TXT_LAYOUT</t>
+          <t>TXT_TILEMAP</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Layout</t>
+          <t>Tilemap</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TXT_PLAYABLES</t>
+          <t>TXT_LAYOUT</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Playables</t>
+          <t>Layout</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TXT_MISCELLANEOUS</t>
+          <t>TXT_PLAYABLES</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Playables</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TXT_SCRIPTS</t>
+          <t>TXT_MISCELLANEOUS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Scripts</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TXT_VISUAL_SCRIPTING</t>
+          <t>TXT_SCRIPTS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Visual Scripting</t>
+          <t>Scripts</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TXT_EVENT</t>
+          <t>TXT_VISUAL_SCRIPTING</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Visual Scripting</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TXT_NEXT_WINDOW</t>
+          <t>TXT_EVENT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>下一个窗口</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TXT_PREV_WINDOW</t>
+          <t>TXT_NEXT_WINDOW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>上一个窗口</t>
+          <t>下一个窗口</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TXT_SEARCH</t>
+          <t>TXT_PREV_WINDOW</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>搜索</t>
+          <t>上一个窗口</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TXT_PACKAGE_MANAGER</t>
+          <t>TXT_SEARCH</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Package Manager</t>
+          <t>搜索</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TXT_ASSET_MANAGEMENT</t>
+          <t>TXT_PACKAGE_MANAGER</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Package Manager</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TXT_TEXT</t>
+          <t>TXT_ASSET_MANAGEMENT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Asset Management</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TXT_TEXT_MESH_PRO</t>
+          <t>TXT_TEXT</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TextMeshPro</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TXT_GENERAL</t>
+          <t>TXT_TEXT_MESH_PRO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>TextMeshPro</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TXT_ANIMATION</t>
+          <t>TXT_GENERAL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>动画</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TXT_SEQUENCING</t>
+          <t>TXT_ANIMATION</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sequencing</t>
+          <t>动画</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TXT_ANALYSIS</t>
+          <t>TXT_SEQUENCING</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>Sequencing</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TXT_AI</t>
+          <t>TXT_ANALYSIS</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>分析</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TXT_HELP</t>
+          <t>TXT_AI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>帮助</t>
+          <t>AI</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TXT_ABOUT</t>
+          <t>TXT_HELP</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>关于</t>
+          <t>帮助</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TXT_USER_MANUAL</t>
+          <t>TXT_ABOUT</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>用户手册</t>
+          <t>关于</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TXT_API_DOCUMENT</t>
+          <t>TXT_USER_MANUAL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>API 文档</t>
+          <t>用户手册</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TXT_FOLDER</t>
+          <t>TXT_API_DOCUMENT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>文件夹</t>
+          <t>API 文档</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TXT_TYPE_SCRIPT</t>
+          <t>TXT_FOLDER</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>文件夹</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TXT_2D</t>
+          <t>TXT_TYPE_SCRIPT</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2D</t>
+          <t>TypeScript</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TXT_SHADER</t>
+          <t>TXT_2D</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>着色器</t>
+          <t>2D</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TXT_SHADER_VARIANT_COLLECTION</t>
+          <t>TXT_SHADER</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>着色器变体收集器</t>
+          <t>着色器</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TXT_TESTING</t>
+          <t>TXT_SHADER_VARIANT_COLLECTION</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>着色器变体收集器</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TXT_DYLIB</t>
+          <t>TXT_TESTING</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>动态库</t>
+          <t>测试</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TXT_DYLIB_REF</t>
+          <t>TXT_DYLIB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>动态库引用</t>
+          <t>动态库</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TXT_SCENE_TEMPLATE</t>
+          <t>TXT_DYLIB_REF</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>场景模版</t>
+          <t>动态库引用</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TXT_SCENE_TEMPLATE_FROM_SCENE</t>
+          <t>TXT_SCENE_TEMPLATE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>来自场景的场景模版</t>
+          <t>场景模版</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TXT_SCENE_TEMPLATE_PIPELINE</t>
+          <t>TXT_SCENE_TEMPLATE_FROM_SCENE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>场景模版管线</t>
+          <t>来自场景的场景模版</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TXT_PREFAB</t>
+          <t>TXT_SCENE_TEMPLATE_PIPELINE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>场景模版管线</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TXT_PREFAB_VARIANT</t>
+          <t>TXT_PREFAB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>预制体变体</t>
+          <t>预制体</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TXT_AUDIO_MIXER</t>
+          <t>TXT_PREFAB_VARIANT</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>音效混合</t>
+          <t>预制体变体</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TXT_MATERIAL</t>
+          <t>TXT_AUDIO_MIXER</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>材质</t>
+          <t>音效混合</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TXT_LENS_FLARE</t>
+          <t>TXT_MATERIAL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lens Flare</t>
+          <t>材质</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TXT_RENDER_TEXTURE</t>
+          <t>TXT_LENS_FLARE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>渲染纹理</t>
+          <t>Lens Flare</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TXT_LIGHTMAP_PARAMETERS</t>
+          <t>TXT_RENDER_TEXTURE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>光照贴图参数</t>
+          <t>渲染纹理</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TXT_LIGHTING_SETTINGS</t>
+          <t>TXT_LIGHTMAP_PARAMETERS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>光照设置</t>
+          <t>光照贴图参数</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TXT_CUSTOM_RENDER_TEXTURE</t>
+          <t>TXT_LIGHTING_SETTINGS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>自定义渲染纹理</t>
+          <t>光照设置</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TXT_ANIMATOR_CONTROLLER</t>
+          <t>TXT_CUSTOM_RENDER_TEXTURE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Animator Controller</t>
+          <t>自定义渲染纹理</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TXT_ANIMATOR_OVERRIDE_CONTROLLER</t>
+          <t>TXT_ANIMATOR_CONTROLLER</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Animator Override Controller</t>
+          <t>Animator Controller</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TXT_AVATAR_MASK</t>
+          <t>TXT_ANIMATOR_OVERRIDE_CONTROLLER</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Avatar Mask</t>
+          <t>Animator Override Controller</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TXT_TIMELINE</t>
+          <t>TXT_AVATAR_MASK</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Timeline</t>
+          <t>Avatar Mask</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TXT_SIGNAL</t>
+          <t>TXT_TIMELINE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>信号</t>
+          <t>Timeline</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TXT_PHYSIC_MATERIAL</t>
+          <t>TXT_SIGNAL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>物理材质</t>
+          <t>信号</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TXT_GUI_SKIN</t>
+          <t>TXT_PHYSIC_MATERIAL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GUI Skin</t>
+          <t>物理材质</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TXT_CUSTOM_FONT</t>
+          <t>TXT_GUI_SKIN</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>自定义字体</t>
+          <t>GUI Skin</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TXT_LEGACY</t>
+          <t>TXT_CUSTOM_FONT</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>传统(Legacy)</t>
+          <t>自定义字体</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TXT_BRUSH</t>
+          <t>TXT_LEGACY</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>刷子</t>
+          <t>传统(Legacy)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TXT_TERRAIN_LAYER</t>
+          <t>TXT_BRUSH</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>地形层</t>
+          <t>刷子</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TXT_CUSTOM_PACKAGE</t>
+          <t>TXT_TERRAIN_LAYER</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>自定义 Package</t>
+          <t>地形层</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TXT_PHYSICS_MATERIAL_2D</t>
+          <t>TXT_CUSTOM_PACKAGE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Physics Material 2D</t>
+          <t>自定义 Package</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TXT_STATE_GRAPH</t>
+          <t>TXT_PHYSICS_MATERIAL_2D</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>状态图</t>
+          <t>Physics Material 2D</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TXT_SCRIPT_GRAPH</t>
+          <t>TXT_STATE_GRAPH</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>脚本图</t>
+          <t>状态图</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TXT_STANDARD_SURFACE_SHADER</t>
+          <t>TXT_SCRIPT_GRAPH</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Standard Surface Shader</t>
+          <t>脚本图</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TXT_UNLIT_SHADER</t>
+          <t>TXT_STANDARD_SURFACE_SHADER</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Unlit Shader</t>
+          <t>Standard Surface Shader</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TXT_IMAGE_EFFECT_SHADER</t>
+          <t>TXT_UNLIT_SHADER</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Image Effect Shader</t>
+          <t>Unlit Shader</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TXT_COMPUTE_SHADER</t>
+          <t>TXT_IMAGE_EFFECT_SHADER</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Compute Shader</t>
+          <t>Image Effect Shader</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TXT_RAY_TRACING_SHADER</t>
+          <t>TXT_COMPUTE_SHADER</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ray Tracing Shader</t>
+          <t>Compute Shader</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXT_OK</t>
+          <t>TXT_RAY_TRACING_SHADER</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>确定</t>
+          <t>Ray Tracing Shader</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXT_CANCEL</t>
+          <t>TXT_OK</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>确定</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TXT_SAVE_EXIT</t>
+          <t>TXT_CANCEL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>保存并退出</t>
+          <t>取消</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TXT_CLOSE</t>
+          <t>TXT_SAVE_EXIT</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>保存并退出</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TXT_INFO</t>
+          <t>TXT_CLOSE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>信息</t>
+          <t>关闭</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TXT_WARNING</t>
+          <t>TXT_INFO</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>警告</t>
+          <t>信息</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TXT_ERROR</t>
+          <t>TXT_WARNING</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>错误</t>
+          <t>警告</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TXT_HINT</t>
+          <t>TXT_ERROR</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>提醒</t>
+          <t>错误</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
+          <t>TXT_HINT</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>提醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
           <t>TXT_HINT_UNSAVE</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>文件未保存，确定退出？</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
+++ b/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B184"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
@@ -2621,6 +2633,102 @@
       <c r="B184" t="inlineStr">
         <is>
           <t>文件未保存，确定退出？</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>TXT_EXTERNAL_TOOLS</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>外部工具</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TXT_EXTERNAL_SCRIPT_EDITOR</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>外部脚本编辑器</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>TXT_BROWSE</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>浏览...</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TXT_IDE_SYSTEM_DEFAULT</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>系统默认</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>TXT_OPEN_CPP_PROJECT_FAILED</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>无法生成 C++ 工程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TXT_OPEN_CPP_PROJECT_NO_SCRIPTS</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>当前工程没有 C++ 源码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>TXT_OPEN_CPP_PROJECT_NO_SLN</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>未找到 Visual Studio 解决方案。请确认编辑器使用 Visual Studio CMake 生成器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>TXT_OPEN_CPP_PROJECT_IDE_FAILED</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>启动 IDE 失败。</t>
         </is>
       </c>
     </row>

--- a/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
+++ b/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B192"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2732,6 +2732,18 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TXT_CPP_CLASS</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>C++ 类</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
+++ b/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2744,6 +2744,18 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TXT_COMPILE_SCRIPTS</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>编译脚本</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
+++ b/source/Tools/LanguageGenerator/Editor/lang-zh-hans.xlsx
@@ -2699,7 +2699,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TXT_OPEN_CPP_PROJECT_NO_SCRIPTS</t>
+          <t>TXT_OPEN_CPP_PROJECT_NO_CPP_SOURCES</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -2747,12 +2747,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TXT_COMPILE_SCRIPTS</t>
+          <t>TXT_COMPILE_CPP</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>编译脚本</t>
+          <t>编译 C++</t>
         </is>
       </c>
     </row>
